--- a/artfynd/A 45564-2024 artfynd.xlsx
+++ b/artfynd/A 45564-2024 artfynd.xlsx
@@ -1895,10 +1895,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122743097</v>
+        <v>122743098</v>
       </c>
       <c r="B12" t="n">
-        <v>79844</v>
+        <v>79847</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1911,34 +1911,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stormyrberget V, Jmt</t>
+          <t>Nedre Rosinedal SV, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
         <v>494061</v>
       </c>
       <c r="R12" t="n">
-        <v>7123037</v>
+        <v>7123035</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122743100</v>
+        <v>122743101</v>
       </c>
       <c r="B13" t="n">
-        <v>79843</v>
+        <v>79848</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494037</v>
+        <v>494041</v>
       </c>
       <c r="R13" t="n">
-        <v>7123103</v>
+        <v>7123109</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2107,10 +2107,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122743101</v>
+        <v>122743100</v>
       </c>
       <c r="B14" t="n">
-        <v>79844</v>
+        <v>79847</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2123,21 +2123,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2147,10 +2147,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494041</v>
+        <v>494037</v>
       </c>
       <c r="R14" t="n">
-        <v>7123109</v>
+        <v>7123103</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2213,10 +2213,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122743098</v>
+        <v>122743097</v>
       </c>
       <c r="B15" t="n">
-        <v>79843</v>
+        <v>79848</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2229,34 +2229,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Nedre Rosinedal SV, Jmt</t>
+          <t>Stormyrberget V, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
         <v>494061</v>
       </c>
       <c r="R15" t="n">
-        <v>7123035</v>
+        <v>7123037</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 45564-2024 artfynd.xlsx
+++ b/artfynd/A 45564-2024 artfynd.xlsx
@@ -1895,10 +1895,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122743098</v>
+        <v>122743097</v>
       </c>
       <c r="B12" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1911,34 +1911,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Nedre Rosinedal SV, Jmt</t>
+          <t>Stormyrberget V, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
         <v>494061</v>
       </c>
       <c r="R12" t="n">
-        <v>7123035</v>
+        <v>7123037</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122743101</v>
+        <v>122743100</v>
       </c>
       <c r="B13" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494041</v>
+        <v>494037</v>
       </c>
       <c r="R13" t="n">
-        <v>7123109</v>
+        <v>7123103</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2107,10 +2107,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122743100</v>
+        <v>122743101</v>
       </c>
       <c r="B14" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2123,21 +2123,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2147,10 +2147,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494037</v>
+        <v>494041</v>
       </c>
       <c r="R14" t="n">
-        <v>7123103</v>
+        <v>7123109</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2213,10 +2213,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122743097</v>
+        <v>122743098</v>
       </c>
       <c r="B15" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2229,34 +2229,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stormyrberget V, Jmt</t>
+          <t>Nedre Rosinedal SV, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
         <v>494061</v>
       </c>
       <c r="R15" t="n">
-        <v>7123037</v>
+        <v>7123035</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 45564-2024 artfynd.xlsx
+++ b/artfynd/A 45564-2024 artfynd.xlsx
@@ -2001,7 +2001,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122743100</v>
+        <v>122743098</v>
       </c>
       <c r="B13" t="n">
         <v>79847</v>
@@ -2037,14 +2037,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stormyrberget SV, Jmt</t>
+          <t>Nedre Rosinedal SV, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494037</v>
+        <v>494061</v>
       </c>
       <c r="R13" t="n">
-        <v>7123103</v>
+        <v>7123035</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2213,7 +2213,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122743098</v>
+        <v>122743100</v>
       </c>
       <c r="B15" t="n">
         <v>79847</v>
@@ -2249,14 +2249,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Nedre Rosinedal SV, Jmt</t>
+          <t>Stormyrberget SV, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494061</v>
+        <v>494037</v>
       </c>
       <c r="R15" t="n">
-        <v>7123035</v>
+        <v>7123103</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 45564-2024 artfynd.xlsx
+++ b/artfynd/A 45564-2024 artfynd.xlsx
@@ -1895,10 +1895,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122743097</v>
+        <v>122743100</v>
       </c>
       <c r="B12" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1911,34 +1911,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stormyrberget V, Jmt</t>
+          <t>Stormyrberget SV, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494061</v>
+        <v>494037</v>
       </c>
       <c r="R12" t="n">
-        <v>7123037</v>
+        <v>7123103</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2107,7 +2107,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122743101</v>
+        <v>122743097</v>
       </c>
       <c r="B14" t="n">
         <v>79848</v>
@@ -2143,14 +2143,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stormyrberget SV, Jmt</t>
+          <t>Stormyrberget V, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494041</v>
+        <v>494061</v>
       </c>
       <c r="R14" t="n">
-        <v>7123109</v>
+        <v>7123037</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2213,10 +2213,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122743100</v>
+        <v>122743101</v>
       </c>
       <c r="B15" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2229,21 +2229,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2253,10 +2253,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494037</v>
+        <v>494041</v>
       </c>
       <c r="R15" t="n">
-        <v>7123103</v>
+        <v>7123109</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 45564-2024 artfynd.xlsx
+++ b/artfynd/A 45564-2024 artfynd.xlsx
@@ -1895,7 +1895,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122743100</v>
+        <v>122743098</v>
       </c>
       <c r="B12" t="n">
         <v>79847</v>
@@ -1931,14 +1931,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stormyrberget SV, Jmt</t>
+          <t>Nedre Rosinedal SV, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494037</v>
+        <v>494061</v>
       </c>
       <c r="R12" t="n">
-        <v>7123103</v>
+        <v>7123035</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2001,7 +2001,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122743098</v>
+        <v>122743100</v>
       </c>
       <c r="B13" t="n">
         <v>79847</v>
@@ -2037,14 +2037,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Nedre Rosinedal SV, Jmt</t>
+          <t>Stormyrberget SV, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494061</v>
+        <v>494037</v>
       </c>
       <c r="R13" t="n">
-        <v>7123035</v>
+        <v>7123103</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 45564-2024 artfynd.xlsx
+++ b/artfynd/A 45564-2024 artfynd.xlsx
@@ -1895,7 +1895,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122743098</v>
+        <v>122743100</v>
       </c>
       <c r="B12" t="n">
         <v>79847</v>
@@ -1931,14 +1931,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Nedre Rosinedal SV, Jmt</t>
+          <t>Stormyrberget SV, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494061</v>
+        <v>494037</v>
       </c>
       <c r="R12" t="n">
-        <v>7123035</v>
+        <v>7123103</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2001,7 +2001,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122743100</v>
+        <v>122743098</v>
       </c>
       <c r="B13" t="n">
         <v>79847</v>
@@ -2037,14 +2037,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stormyrberget SV, Jmt</t>
+          <t>Nedre Rosinedal SV, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494037</v>
+        <v>494061</v>
       </c>
       <c r="R13" t="n">
-        <v>7123103</v>
+        <v>7123035</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 45564-2024 artfynd.xlsx
+++ b/artfynd/A 45564-2024 artfynd.xlsx
@@ -2001,10 +2001,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122743098</v>
+        <v>122743101</v>
       </c>
       <c r="B13" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2017,34 +2017,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Nedre Rosinedal SV, Jmt</t>
+          <t>Stormyrberget SV, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494061</v>
+        <v>494041</v>
       </c>
       <c r="R13" t="n">
-        <v>7123035</v>
+        <v>7123109</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2107,10 +2107,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122743097</v>
+        <v>122743098</v>
       </c>
       <c r="B14" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2123,34 +2123,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stormyrberget V, Jmt</t>
+          <t>Nedre Rosinedal SV, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
         <v>494061</v>
       </c>
       <c r="R14" t="n">
-        <v>7123037</v>
+        <v>7123035</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2213,7 +2213,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122743101</v>
+        <v>122743097</v>
       </c>
       <c r="B15" t="n">
         <v>79848</v>
@@ -2249,14 +2249,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stormyrberget SV, Jmt</t>
+          <t>Stormyrberget V, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494041</v>
+        <v>494061</v>
       </c>
       <c r="R15" t="n">
-        <v>7123109</v>
+        <v>7123037</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 45564-2024 artfynd.xlsx
+++ b/artfynd/A 45564-2024 artfynd.xlsx
@@ -1895,10 +1895,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122743100</v>
+        <v>122743101</v>
       </c>
       <c r="B12" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1911,21 +1911,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1935,10 +1935,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494037</v>
+        <v>494041</v>
       </c>
       <c r="R12" t="n">
-        <v>7123103</v>
+        <v>7123109</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122743101</v>
+        <v>122743100</v>
       </c>
       <c r="B13" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494041</v>
+        <v>494037</v>
       </c>
       <c r="R13" t="n">
-        <v>7123109</v>
+        <v>7123103</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 45564-2024 artfynd.xlsx
+++ b/artfynd/A 45564-2024 artfynd.xlsx
@@ -1895,7 +1895,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122743101</v>
+        <v>122743097</v>
       </c>
       <c r="B12" t="n">
         <v>79848</v>
@@ -1931,14 +1931,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stormyrberget SV, Jmt</t>
+          <t>Stormyrberget V, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494041</v>
+        <v>494061</v>
       </c>
       <c r="R12" t="n">
-        <v>7123109</v>
+        <v>7123037</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2001,7 +2001,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122743100</v>
+        <v>122743098</v>
       </c>
       <c r="B13" t="n">
         <v>79847</v>
@@ -2037,14 +2037,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stormyrberget SV, Jmt</t>
+          <t>Nedre Rosinedal SV, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494037</v>
+        <v>494061</v>
       </c>
       <c r="R13" t="n">
-        <v>7123103</v>
+        <v>7123035</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2107,10 +2107,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122743098</v>
+        <v>122743101</v>
       </c>
       <c r="B14" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2123,34 +2123,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nedre Rosinedal SV, Jmt</t>
+          <t>Stormyrberget SV, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494061</v>
+        <v>494041</v>
       </c>
       <c r="R14" t="n">
-        <v>7123035</v>
+        <v>7123109</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2213,10 +2213,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122743097</v>
+        <v>122743100</v>
       </c>
       <c r="B15" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2229,34 +2229,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stormyrberget V, Jmt</t>
+          <t>Stormyrberget SV, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494061</v>
+        <v>494037</v>
       </c>
       <c r="R15" t="n">
-        <v>7123037</v>
+        <v>7123103</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 45564-2024 artfynd.xlsx
+++ b/artfynd/A 45564-2024 artfynd.xlsx
@@ -1895,10 +1895,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122743097</v>
+        <v>122743098</v>
       </c>
       <c r="B12" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1911,34 +1911,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stormyrberget V, Jmt</t>
+          <t>Nedre Rosinedal SV, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
         <v>494061</v>
       </c>
       <c r="R12" t="n">
-        <v>7123037</v>
+        <v>7123035</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2001,7 +2001,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122743098</v>
+        <v>122743100</v>
       </c>
       <c r="B13" t="n">
         <v>79847</v>
@@ -2037,14 +2037,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Nedre Rosinedal SV, Jmt</t>
+          <t>Stormyrberget SV, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494061</v>
+        <v>494037</v>
       </c>
       <c r="R13" t="n">
-        <v>7123035</v>
+        <v>7123103</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2107,7 +2107,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122743101</v>
+        <v>122743097</v>
       </c>
       <c r="B14" t="n">
         <v>79848</v>
@@ -2143,14 +2143,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stormyrberget SV, Jmt</t>
+          <t>Stormyrberget V, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494041</v>
+        <v>494061</v>
       </c>
       <c r="R14" t="n">
-        <v>7123109</v>
+        <v>7123037</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2213,10 +2213,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122743100</v>
+        <v>122743101</v>
       </c>
       <c r="B15" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2229,21 +2229,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2253,10 +2253,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494037</v>
+        <v>494041</v>
       </c>
       <c r="R15" t="n">
-        <v>7123103</v>
+        <v>7123109</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 45564-2024 artfynd.xlsx
+++ b/artfynd/A 45564-2024 artfynd.xlsx
@@ -2107,7 +2107,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122743097</v>
+        <v>122743101</v>
       </c>
       <c r="B14" t="n">
         <v>79848</v>
@@ -2143,14 +2143,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stormyrberget V, Jmt</t>
+          <t>Stormyrberget SV, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494061</v>
+        <v>494041</v>
       </c>
       <c r="R14" t="n">
-        <v>7123037</v>
+        <v>7123109</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2213,7 +2213,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122743101</v>
+        <v>122743097</v>
       </c>
       <c r="B15" t="n">
         <v>79848</v>
@@ -2249,14 +2249,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stormyrberget SV, Jmt</t>
+          <t>Stormyrberget V, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494041</v>
+        <v>494061</v>
       </c>
       <c r="R15" t="n">
-        <v>7123109</v>
+        <v>7123037</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 45564-2024 artfynd.xlsx
+++ b/artfynd/A 45564-2024 artfynd.xlsx
@@ -1895,10 +1895,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122743098</v>
+        <v>122743100</v>
       </c>
       <c r="B12" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1931,14 +1931,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Nedre Rosinedal SV, Jmt</t>
+          <t>Stormyrberget SV, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494061</v>
+        <v>494037</v>
       </c>
       <c r="R12" t="n">
-        <v>7123035</v>
+        <v>7123103</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122743100</v>
+        <v>122743098</v>
       </c>
       <c r="B13" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2037,14 +2037,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stormyrberget SV, Jmt</t>
+          <t>Nedre Rosinedal SV, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494037</v>
+        <v>494061</v>
       </c>
       <c r="R13" t="n">
-        <v>7123103</v>
+        <v>7123035</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2110,7 +2110,7 @@
         <v>122743101</v>
       </c>
       <c r="B14" t="n">
-        <v>79848</v>
+        <v>79851</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         <v>122743097</v>
       </c>
       <c r="B15" t="n">
-        <v>79848</v>
+        <v>79851</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 45564-2024 artfynd.xlsx
+++ b/artfynd/A 45564-2024 artfynd.xlsx
@@ -1895,10 +1895,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122743100</v>
+        <v>122743098</v>
       </c>
       <c r="B12" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1931,14 +1931,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stormyrberget SV, Jmt</t>
+          <t>Nedre Rosinedal SV, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494037</v>
+        <v>494061</v>
       </c>
       <c r="R12" t="n">
-        <v>7123103</v>
+        <v>7123035</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122743098</v>
+        <v>122743100</v>
       </c>
       <c r="B13" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2037,14 +2037,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Nedre Rosinedal SV, Jmt</t>
+          <t>Stormyrberget SV, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494061</v>
+        <v>494037</v>
       </c>
       <c r="R13" t="n">
-        <v>7123035</v>
+        <v>7123103</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2110,7 +2110,7 @@
         <v>122743101</v>
       </c>
       <c r="B14" t="n">
-        <v>79851</v>
+        <v>79853</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         <v>122743097</v>
       </c>
       <c r="B15" t="n">
-        <v>79851</v>
+        <v>79853</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 45564-2024 artfynd.xlsx
+++ b/artfynd/A 45564-2024 artfynd.xlsx
@@ -2319,10 +2319,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124467413</v>
+        <v>124467403</v>
       </c>
       <c r="B16" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2335,21 +2335,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494087</v>
+        <v>494063</v>
       </c>
       <c r="R16" t="n">
-        <v>7123048</v>
+        <v>7123052</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2395,6 +2395,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2421,10 +2426,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124467403</v>
+        <v>124467413</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2437,21 +2442,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2461,10 +2466,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494063</v>
+        <v>494087</v>
       </c>
       <c r="R17" t="n">
-        <v>7123052</v>
+        <v>7123048</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2497,11 +2502,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 45564-2024 artfynd.xlsx
+++ b/artfynd/A 45564-2024 artfynd.xlsx
@@ -2319,10 +2319,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124467403</v>
+        <v>124467413</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2335,21 +2335,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494063</v>
+        <v>494087</v>
       </c>
       <c r="R16" t="n">
-        <v>7123052</v>
+        <v>7123048</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2395,11 +2395,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2426,10 +2421,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124467413</v>
+        <v>124467403</v>
       </c>
       <c r="B17" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2442,21 +2437,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2466,10 +2461,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494087</v>
+        <v>494063</v>
       </c>
       <c r="R17" t="n">
-        <v>7123048</v>
+        <v>7123052</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2502,6 +2497,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 45564-2024 artfynd.xlsx
+++ b/artfynd/A 45564-2024 artfynd.xlsx
@@ -2428,7 +2428,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">

--- a/artfynd/A 45564-2024 artfynd.xlsx
+++ b/artfynd/A 45564-2024 artfynd.xlsx
@@ -2424,7 +2424,7 @@
         <v>124467403</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
